--- a/reports/module-data-integration-audit/2026-07-27/CROSS_MODULE_IDENTITY_COLLISION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CROSS_MODULE_IDENTITY_COLLISION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Collisions" sheetId="1" r:id="Ra8753537d24e41c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Collisions" sheetId="1" r:id="Rf613096004a54881"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -344,7 +344,7 @@
         <x:v>Moves; Source; Tower</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>public.move_artifact_review_decisions; public.move_artifacts; public.move_dependencies; public.move_instances; public.move_template_audit_log; public.program_evidence_reviews; public.ai_control_sources; public.client; public.data_inventory_records; public.data_sources; public.enterprise_context_chunks; public.enterprise_context_source_files; public.enterprise_context_sources; public.evidence; public.external_sources; public.home_knowledge_evidence_sources; public.person_client_memberships; public.source_artifact_chunks</x:v>
+        <x:v>public.move_artifact_review_decisions; public.move_artifacts; public.move_dependencies; public.move_instances; public.move_template_audit_log; public.program_evidence_reviews; public.ai_control_sources; public.data_inventory_records; public.data_sources; public.enterprise_context_chunks; public.enterprise_context_source_files; public.enterprise_context_sources; public.evidence; public.external_sources; public.home_knowledge_evidence_sources; public.person_client_memberships; public.source_artifact_chunks; public.source_artifact_facts</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>High</x:v>
@@ -364,7 +364,7 @@
         <x:v>Source; Tower</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>public.source_commercial_exceptions; public.source_contract_optimization_profiles; public.source_event_pricing_submissions; public.source_pricing_components; public.source_vendor_commitments; public.source_vendor_proposal_fact_reviews; public.source_vendor_proposal_facts; public.vendor; public.Vendor; public.vendor_comparison; public.vendor_contracts; public.vendors; public.application_portfolio; public.tower_program_financials; public.tower_read_model_vendors; public.tower_vendor_spend; vendors.renewal_date</x:v>
+        <x:v>public.source_commercial_exceptions; public.source_contract_optimization_profiles; public.source_event_pricing_submissions; public.source_pricing_components; public.source_vendor_commitments; public.source_vendor_proposal_fact_reviews; public.source_vendor_proposal_facts; public.vendor_contracts; public.application_portfolio; public.tower_program_financials; public.tower_read_model_vendors; public.tower_vendor_spend</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>Medium</x:v>
@@ -384,7 +384,7 @@
         <x:v>Source; Tower</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>public.agreement; public.contract; public.CONTRACT_TERMS_V1; public.contracting; public.contractor; public.contractual; public.source_contract_evidence_manifests; public.source_contract_evidence_metrics; public.source_contract_evidence_rows; public.source_contract_optimization_findings; public.source_contract_optimization_levers; public.source_contract_optimization_profiles; public.vendor_contracts; cio_tower.answer_traces; cio_tower.prompt_packages; cio_tower.question_contracts; intelligence_v7.active_tenant_contract_versions; public.ai_control_spend_contracts</x:v>
+        <x:v>public.source_contract_evidence_manifests; public.source_contract_evidence_metrics; public.source_contract_evidence_rows; public.source_contract_optimization_findings; public.source_contract_optimization_levers; public.source_contract_optimization_profiles; public.vendor_contracts; cio_tower.answer_traces; cio_tower.prompt_packages; cio_tower.question_contracts; intelligence_v7.active_tenant_contract_versions; public.ai_control_spend_contracts</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>Medium</x:v>
@@ -404,7 +404,7 @@
         <x:v>Moves; Source; Tower</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>public.Move; public.move_artifact_review_decisions; public.move_artifacts; public.move_dependencies; public.move_instances; public.move_template_artifacts; public.move_template_audit_log; public.move_template_gates; public.move_template_review_state; public.move_template_versions; public.move_templates; public.Moves; public.program_evidence_reviews; public.source_events; public.source_value_lines; cio_tower.mart_program_decision_lanes; cio_tower.tool_identity_aliases; public.ai_control_benefit_realization</x:v>
+        <x:v>public.move_artifact_review_decisions; public.move_artifacts; public.move_dependencies; public.move_instances; public.move_template_artifacts; public.move_template_audit_log; public.move_template_gates; public.move_template_review_state; public.move_template_versions; public.move_templates; public.program_evidence_reviews; public.source_events; public.source_value_lines; cio_tower.mart_program_decision_lanes; cio_tower.tool_identity_aliases; public.ai_control_benefit_realization; public.ai_control_initiatives; public.ai_control_persona_productivity</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>High</x:v>
@@ -421,13 +421,13 @@
         <x:v>Application/System</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>Moves; Source; Tower</x:v>
+        <x:v>Source; Tower</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>public.approved; public.ITSM; public.source_event_approvals; public.system; public.uncapped; public.application; public.application_portfolio; public.ItsmRecord; public.system_refs; public.tower_cmdb_cis; public.tower_cmdb_dependencies; public.tower_itsm_records</x:v>
+        <x:v>public.source_event_approvals; public.application_portfolio; public.tower_cmdb_cis; public.tower_cmdb_dependencies; public.tower_itsm_records</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>Preserve local IDs; map reviewed objects through governance.object_identity_map before cross-module use.</x:v>
@@ -444,7 +444,7 @@
         <x:v>Source; Tower</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>public.cost; public.outcome; public.PHASE_C_VALUE_MODES; public.SLA; public.source_contract_evidence_metrics; public.source_meeting_outcomes; public.source_value_chain; public.source_value_levers; public.source_value_lines; public.source_value_states; public.value; public.value_source; public.valueType; cio_tower.mart_value_funnel; public.ai_control_agent_outcomes; public.ai_control_benefit_realization; public.ai_control_dora_metrics; public.ai_control_initiatives</x:v>
+        <x:v>public.source_contract_evidence_metrics; public.source_meeting_outcomes; public.source_value_chain; public.source_value_levers; public.source_value_lines; public.source_value_states; cio_tower.facts; cio_tower.mart_value_funnel; cio_tower.measure_results; cio_tower.measures; public.ai_control_agent_outcomes; public.ai_control_benefit_realization; public.ai_control_dora_metrics; public.ai_control_initiatives; public.ai_control_persona_productivity; public.ai_control_spend_contracts; public.dora_baselines; public.tower_budget_rollups</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>Medium</x:v>
@@ -464,7 +464,7 @@
         <x:v>Moves; Source; Tower</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>public.move_artifact_review_decisions; public.decision; public.decision_owner; public.source_event_approvals; public.source_event_gate_criterion_states; cio_tower.mart_program_decision_lanes</x:v>
+        <x:v>public.move_artifact_review_decisions; public.source_event_approvals; public.source_event_gate_criterion_states; cio_tower.mart_program_decision_lanes</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
         <x:v>High</x:v>
@@ -484,7 +484,7 @@
         <x:v>Source; Tower</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>public.ai_control_sources; public.risk; public.risks; public.ai_control_actions; public.ai_control_agent_outcomes; public.ai_control_atlas_context_packs; public.ai_control_benefit_realization; public.ai_control_context_facts; public.ai_control_context_relationships; public.ai_control_dora_metrics; public.ai_control_evidence_items; public.ai_control_initiatives; public.ai_control_persona_productivity; public.ai_control_refresh_runs; public.ai_control_risk_governance; public.ai_control_spend_contracts; public.ai_control_tool_usage_monthly; public.ai_control_tower_lens_mv</x:v>
+        <x:v>public.ai_control_sources; public.ai_control_actions; public.ai_control_agent_outcomes; public.ai_control_atlas_context_packs; public.ai_control_benefit_realization; public.ai_control_context_facts; public.ai_control_context_relationships; public.ai_control_dora_metrics; public.ai_control_evidence_items; public.ai_control_initiatives; public.ai_control_persona_productivity; public.ai_control_refresh_runs; public.ai_control_risk_governance; public.ai_control_spend_contracts; public.ai_control_tool_usage_monthly; public.ai_control_tower_lens_mv</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>Medium</x:v>
@@ -504,7 +504,7 @@
         <x:v>Moves; Source; Tower</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>public.move_artifact_review_decisions; public.move_artifacts; public.move_template_artifacts; public.program_evidence_reviews; public.source; public.ai_control_sources; public.artifact; public.buildSourceEvidenceReadiness; public.data_sources; public.enterprise_context_chunks; public.enterprise_context_source_files; public.enterprise_context_sources; public.evidence; public.EvidenceItem; public.external_sources; public.home_knowledge_evidence_sources; public.knowledge_sources; public.source_artifact_acceptances</x:v>
+        <x:v>public.move_artifact_review_decisions; public.move_artifacts; public.move_template_artifacts; public.program_evidence_reviews; public.ai_control_sources; public.data_sources; public.enterprise_context_chunks; public.enterprise_context_source_files; public.enterprise_context_sources; public.evidence; public.external_sources; public.home_knowledge_evidence_sources; public.knowledge_sources; public.source_artifact_acceptances; public.source_artifact_chunks; public.source_artifact_facts; public.source_artifact_generation_jobs; public.source_artifacts</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>High</x:v>

--- a/reports/module-data-integration-audit/2026-07-27/CROSS_MODULE_IDENTITY_COLLISION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CROSS_MODULE_IDENTITY_COLLISION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Collisions" sheetId="1" r:id="Rf613096004a54881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Collisions" sheetId="1" r:id="R6f68a6510a604584"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/reports/module-data-integration-audit/2026-07-27/CROSS_MODULE_IDENTITY_COLLISION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CROSS_MODULE_IDENTITY_COLLISION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Collisions" sheetId="1" r:id="R6f68a6510a604584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Collisions" sheetId="1" r:id="R684d7492d3064d98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -444,7 +444,7 @@
         <x:v>Source; Tower</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>public.source_contract_evidence_metrics; public.source_meeting_outcomes; public.source_value_chain; public.source_value_levers; public.source_value_lines; public.source_value_states; cio_tower.facts; cio_tower.mart_value_funnel; cio_tower.measure_results; cio_tower.measures; public.ai_control_agent_outcomes; public.ai_control_benefit_realization; public.ai_control_dora_metrics; public.ai_control_initiatives; public.ai_control_persona_productivity; public.ai_control_spend_contracts; public.dora_baselines; public.tower_budget_rollups</x:v>
+        <x:v>public.source_contract_evidence_metrics; public.source_contract_optimization_levers; public.source_meeting_outcomes; public.source_value_chain; public.source_value_levers; public.source_value_lines; public.source_value_states; cio_tower.facts; cio_tower.mart_value_funnel; cio_tower.measure_results; cio_tower.measures; public.ai_control_agent_outcomes; public.ai_control_benefit_realization; public.ai_control_dora_metrics; public.ai_control_initiatives; public.ai_control_persona_productivity; public.ai_control_spend_contracts; public.ai_control_tool_usage_monthly</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>Medium</x:v>
@@ -464,7 +464,7 @@
         <x:v>Moves; Source; Tower</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>public.move_artifact_review_decisions; public.source_event_approvals; public.source_event_gate_criterion_states; cio_tower.mart_program_decision_lanes</x:v>
+        <x:v>public.move_artifact_review_decisions; public.source_event_approvals; public.source_event_gate_criterion_states; cio_tower.mart_program_decision_lanes; public.ai_control_actions</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
         <x:v>High</x:v>
